--- a/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
@@ -7427,7 +7427,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-11 23:52 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-11 23:55 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>

--- a/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
@@ -28,6 +28,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stop-Loss Backtests" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Examples" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -940,104 +941,116 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Worked Examples</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>The arithmetic behind each headline metric, recalculated with this portfolio's own numbers.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Severity legend (used by Rule Flags and Data Quality)</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n"/>
       <c r="B41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>what_it_means</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>The plan fails under the configured rules. Address before relying on any other number.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>A rule is breached in a way that changes the answer. Act on it.</t>
+          <t>The plan fails under the configured rules. Address before relying on any other number.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Outside the configured comfort zone. Review and decide.</t>
+          <t>A rule is breached in a way that changes the answer. Act on it.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Inside the rules but worth watching over time.</t>
+          <t>Outside the configured comfort zone. Review and decide.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Inside the rules but worth watching over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Context, not a problem.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="4" t="n"/>
-    </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Every metric is defined on the Definitions sheet. The same text generates docs/METRIC_DEFINITIONS.md and the web UI Definitions tab.</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6599,7 +6612,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=6733 | inception=2000-01-03 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=6733 | inception=2000-01-03 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6634,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=6733 | inception=2000-01-03 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=6733 | inception=2000-01-03 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6656,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=1307 | inception=2021-07-28 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=1307 | inception=2021-07-28 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6678,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=6089 | inception=2002-07-30 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=6089 | inception=2002-07-30 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6700,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=6089 | inception=2002-07-30 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=6089 | inception=2002-07-30 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6722,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=4046 | inception=2010-09-09 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=4046 | inception=2010-09-09 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6744,7 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=6733 | inception=2000-01-03 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=6733 | inception=2000-01-03 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6766,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>source=cache | rows=5795 | inception=2003-09-29 | as_of=2026-10-09 | cache hit (live, 0.1d old)</t>
+          <t>source=cache | rows=5795 | inception=2003-09-29 | as_of=2026-10-09 | cache hit (live, 0.2d old)</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7440,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-11 23:55 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-12 00:25 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>
@@ -13338,6 +13351,1003 @@
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Worked examples - the arithmetic behind each headline metric, using your own numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>your_numbers</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>what_it_means</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>the_trap</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>what_to_do</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>weights_source</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Weights source</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Which input column was used: explicit portfolio weights, market value / total, or quantity x price.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>7 holdings: ADBE 22.0%, CASH 12.5%, DIS 9.5%, DUOL 13.5%, IEF 4.3%, SHY 13.2%, VOO 25.0%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>supplied</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>These weights are what every simulation starts from. Total invested contributions are $450,000, and the plan's obligation is $441,127.</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Weights are renormalised to 100%. If your weights summed to 92%, everything is scaled up by 8.7% silently.</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>If the source is not what you intended, fix the spreadsheet column rather than the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>hhi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>HHI (concentration index)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Sum of squared weights. Normalised version: (HHI - 1/n) / (1 - 1/n).</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0.220² + 0.125² + 0.095² + 0.135² + 0.043² + 0.132² + 0.250² = 0.1731</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>0.1731</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>With 7 holdings, a perfectly even portfolio would give 0.1429. Yours is 0.1731, so the concentration is real rather than nominal.</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>HHI sees position size only. Two 25% positions in perfectly correlated names look the same as two independent names.</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Use it to argue concentration quantitatively instead of saying 'it feels concentrated'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>effective_n</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Effective number of independent bets</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>1 / HHI, where HHI is the sum of squared weights over all holdings with weight &gt; 0.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>1 / 0.0353 = 5.78</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>You hold 7 positions but they behave like 5.78 independent bets. That is the number the funding probabilities are really built on.</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>It measures weight concentration, not correlation-adjusted independence, so it is an upper bound on real diversification.</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>The rule engine flags it when effective_n falls below 60% of the holding count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>top3_top5_top10</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Top 3 / 5 / 10 weight</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Sum of the largest three, five and ten weights.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>largest VOO 25.0%; top 3 = 60.5% of the portfolio</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Three positions carry 60.5% of the plan. If any one of them halves, the whole terminal value moves by roughly a third of that weight.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>With fewer than 3 holdings the top-3 figure is simply 100%.</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Compare against max_position_weight and max_sector_weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>correlation_cluster</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Correlation cluster</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Single-linkage grouping of holdings joined by correlation above the threshold.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>IEF, SHY move together (mean correlation 0.78) and carry 17.5% together</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Those 2 holdings are one bet. Treat their combined weight as a single exposure when you compare it to the 30.0% group cap.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Single-linkage can chain A-B and B-C into one cluster even when A-C correlation is modest.</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Apply the correlated-group cap to the cluster, not to each member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>required_reserve</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Required reserve (present value)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Payment x [1 - (1+r)^-n] / r x (1+r) for n = last_year - first_year + 1 payments at rate = reserve_discount_rate (annuity-due).</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>$50,000/(1+0.029)^0 + $50,000/(1+0.029)^1 + $50,000/(1+0.029)^2 + $50,000/(1+0.029)^3 + $50,000/(1+0.029)^4 + $50,000/(1+0.029)^5 + $50,000/(1+0.029)^6 + $50,000/(1+0.029)^7 + $50,000/(1+0.029)^8 + $50,000/(1+0.029)^9 … = $441,127</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>$441,127</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>10 payments of $50,000 from 2033 to 2042, discounted at 2.9%, must be standing still in 2033. Everything above that is facility surplus.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>It is a present value, not cash you must hold. A reserve exactly equal to it only works if the reserve keeps earning that rate.</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>If the discount rate is wrong, the obligation is wrong: 2.9% here, so test 2% and 4% before committing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>terminal_percentiles</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Terminal percentiles (p5 ... p95)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Percentiles of the simulated 2033 value distribution.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>10,000 simulated outcomes of the 2033 value: p5=$443,354, p25=$561,481, p50=$662,701, p75=$789,459, p95=$1,009,200</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>$662,701</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>The median is $662,701, but half the runs land below it. Against contributions of $450,000, the 5th percentile is $443,354 - that is the number the reserve decision should be sized from.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Percentiles from 10,000 simulations are stable to roughly +/-0.5pp in probability terms, not to the dollar.</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Fund obligations from p5-p10, plan spending from p50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>prob_terminal_gt_start</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Success: terminal &gt; contributions</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Share of simulations where 2033 value &gt; total contributions (nominal).</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>9432 of 10,000 Monte Carlo paths end above $450,000</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>94.3%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Nominal success looks comfortable at 94.3%. Compare it with the bootstrap figure of 95.6%, which only uses sequences that actually happened.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Growing money in nominal terms while losing purchasing power still counts as success here.</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Always read it next to prob_terminal_gt_real_start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>prob_all_payments_funded</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Probability all reserve payments funded</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Share of simulations where the reserve balance never goes below zero at any of the 10 payment dates.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Monte Carlo: 8340 of 10,000 paths fund all 10 payments; bootstrap: 1943 of 10,000</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>83.4% / 19.4%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>This is the decision metric, and the two engines disagree: 83.4% against 19.4%. Plan against the lower one.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>It requires the reserve to be intact at each payment date; a simulation that ends solvent but was empty in 2037 still fails.</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Below the 90% rule threshold the engine raises a HIGH funding flag: extend the glide path, raise the buffer, or shrink payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>cvar</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>CVaR / expected shortfall</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Negative of the mean of returns at or beyond the VaR quantile.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>average of the worst 5% of bootstrap outcomes = 7.0% of invested capital</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>In the bad tail the average outcome is a loss of 7.0%</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Terminal CVaR is measured on the 2033 outcome relative to contributions over six years, not on a month. It is a horizon loss, not a monthly one. A NEGATIVE CVaR is not an error: it means that even the worst 5% of simulated outcomes are, on average, still gains - the tail is not loss-making under these assumptions.</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>The rule engine raises a HIGH tail flag above 30% terminal CVaR95.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>max_drawdown_growth</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Max drawdown (growth phase)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Deepest peak-to-trough fall in each simulated path before the 2033 split; reported as a median and as probabilities of exceeding 10/20/30/40%.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>across the simulations the median worst peak-to-trough is -14.2% and the worst 5% of paths reach -24.8%</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>-24.8%</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>In the unlucky 5% of paths the portfolio falls 24.8% from its peak before the glide end, against a configured review trigger of 20%.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Measured on the growth phase only. Reserve-phase drawdowns are deliberately excluded because that money is already earmarked.</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Above the 25% review trigger the engine raises a drawdown flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>glide_path</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Glide path targets</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Year-by-year equity/bond/cash targets from glide_path.method between start_equity and end_equity.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2027: equity 70.0% → 2033: equity 35.0%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Equity moves from 70.0% to 35.0% across the plan - this schedule de-risks only if the end target is below the start weight. The simulations follow it mechanically, so changing the 2033 equity target changes every funding probability.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Glide path changes risk, not expected return much. Its value shows up in drawdown and reserve-funding probabilities, not in the median.</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Compare the glide variants table: it re-runs the simulation with no glide path, linear, accelerating and custom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>rebalance_band</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Rebalancing band</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Absolute: target +/- band percentage points. Relative: target x (1 +/- relative_band).</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0 of 3 classes sit outside the ±5.0% band</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>With a 5.0% band and 0.1% transaction cost, 0 classes are currently outside the band.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Bands are tested on asset *class* weights at month end, not on individual holdings.</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Check mean_turnover and mean_rebalances to see what the band actually costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>engine_disagreement</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Engine disagreement spread</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Relative difference between the Monte Carlo and historical bootstrap values of the same metric.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>reserve funding: Monte Carlo 83.4% vs bootstrap 19.4% = a 64.0% spread</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>The engines disagree more than any single holding's weight. That is a statement about the assumptions, not about the portfolio.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>The engines answer different questions, so some spread is expected. Only a spread in a decision-relevant metric matters.</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Report ranges rather than point estimates, and decide on the more conservative engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>bear_ever_prob</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>P(bear at any point 2027-2032)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Share of Markov simulations where at least one growth-phase year lands in bear or severe_bear.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>the regime model puts 61.5% probability on at least one bear year between 2027 and 2032</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>This is not a loss estimate; it is the chance that the plan has to absorb a bad year somewhere in the glide, which is what makes the drawdown numbers worth reading.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>'At least one bear year' is a low bar; 60% here does not mean 60% chance of failure.</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pair it with expected duration and terminal percentiles, not with the headline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>data_provenance</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Data provenance (source / as-of)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Per ticker: cache hit, network download, or committed bundled snapshot, with rows, inception date and data-as-of date.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>prices resolved from: cache (8); earliest as-of 2026-10-09</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>cache</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Two runs of the same portfolio disagree most often because of data vintage, not mathematics. This is the vintage this run used.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Offline reproducibility and live freshness are different goals; the report states which one it used.</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Refresh with `python scripts/build_offline_dataset.py` when you need current prices, or run with --offline for a reproducible result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>max_correlated_group_weight</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>GRP-01 — Correlated group 'Growth/Consumer-Tech' total weight</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Correlated-group exposure &gt; configured cap (30.0%)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>measured 0.4500 against threshold 0.3000</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Group 'Growth/Consumer-Tech' (ADBE, DIS, DUOL) totals 45.0% vs a 30.0% cap.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Correlation is estimated on shared history, so a cluster can be understated when a holding has a short record.</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Trim the 'Growth/Consumer-Tech' group (ADBE, DIS, DUOL) toward 30.0%; these holdings move together and diversification is overstated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>engine_disagreement</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>MODEL-05 — Monte Carlo vs historical bootstrap disagreement</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Key metrics differ materially between Gaussian MC and real-history bootstrap (&gt;10pp probability or &gt;25% value)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>measured 1.0000 against threshold 1.0000</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>reserve funded differs by 64.0%.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>The engines answer different questions, so some spread is expected. Only a spread in a decision-relevant metric matters.</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Report ranges, not point estimates; make reserve/funding decisions using the conservative bootstrap engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>prob_all_payments_funded</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>RESV-04 — Probability all 10 reserve payments funded</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>min(MC, bootstrap) P(all reserve payments funded) &lt; 90.0%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>measured 0.1943 against threshold 0.9000</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>MC 83.4% / bootstrap 19.4% vs a 90.0% planning standard.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>It requires the reserve to be intact at each payment date; a simulation that ends solvent but was empty in 2037 still fails.</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Increase the reserve discount buffer, extend the glide path, or reduce payment size; plan against the conservative engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Deterministic: every line here is recomputed from this run's results. No model and no generated commentary.</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
@@ -7440,7 +7440,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-12 00:25 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-12 00:33 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>

--- a/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/web/variant/spreadsheet/portfolio_analysis.xlsx
@@ -7440,7 +7440,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-12 00:33 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-12 00:37 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>
